--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,6 +877,804 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134096911</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58508</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hedsåsen 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>333627</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6434088</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134097064</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58125</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hedsåsen 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>333627</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6434088</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134096724</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58249</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hedsåsen 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>333627</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6434088</v>
+      </c>
+      <c r="S6" t="n">
+        <v>100</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134096807</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58123</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hedsåsen 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>333627</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6434088</v>
+      </c>
+      <c r="S7" t="n">
+        <v>100</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134096944</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hedsåsen 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>333627</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6434088</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134096867</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58687</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hedsåsen 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>333627</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6434088</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134097045</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58613</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hedsåsen 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>333627</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6434088</v>
+      </c>
+      <c r="S10" t="n">
+        <v>100</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>134096911</v>
       </c>
       <c r="B4" t="n">
-        <v>58508</v>
+        <v>58509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>134097064</v>
       </c>
       <c r="B5" t="n">
-        <v>58125</v>
+        <v>58126</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134096724</v>
+        <v>134096807</v>
       </c>
       <c r="B6" t="n">
-        <v>58249</v>
+        <v>58124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,21 +1118,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103012</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134096807</v>
+        <v>134096724</v>
       </c>
       <c r="B7" t="n">
-        <v>58123</v>
+        <v>58250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1232,21 +1232,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
         <v>134096944</v>
       </c>
       <c r="B8" t="n">
-        <v>57977</v>
+        <v>57978</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>134096867</v>
       </c>
       <c r="B9" t="n">
-        <v>58687</v>
+        <v>58688</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>134097045</v>
       </c>
       <c r="B10" t="n">
-        <v>58613</v>
+        <v>58614</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -882,7 +882,7 @@
         <v>134096911</v>
       </c>
       <c r="B4" t="n">
-        <v>58509</v>
+        <v>58519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>134097064</v>
       </c>
       <c r="B5" t="n">
-        <v>58126</v>
+        <v>58136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         <v>134096807</v>
       </c>
       <c r="B6" t="n">
-        <v>58124</v>
+        <v>58134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>134096724</v>
       </c>
       <c r="B7" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>134096944</v>
       </c>
       <c r="B8" t="n">
-        <v>57978</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>134096867</v>
       </c>
       <c r="B9" t="n">
-        <v>58688</v>
+        <v>58698</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>134097045</v>
       </c>
       <c r="B10" t="n">
-        <v>58614</v>
+        <v>58624</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134096911</v>
+        <v>134096724</v>
       </c>
       <c r="B4" t="n">
-        <v>58519</v>
+        <v>58260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134097064</v>
+        <v>134096807</v>
       </c>
       <c r="B5" t="n">
-        <v>58136</v>
+        <v>58134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1107,27 +1107,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134096807</v>
+        <v>134096911</v>
       </c>
       <c r="B6" t="n">
-        <v>58134</v>
+        <v>58519</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>102990</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134096724</v>
+        <v>134097064</v>
       </c>
       <c r="B7" t="n">
-        <v>58260</v>
+        <v>58136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1232,21 +1232,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -879,32 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134096724</v>
+        <v>134096911</v>
       </c>
       <c r="B4" t="n">
-        <v>58260</v>
+        <v>58519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134096807</v>
+        <v>134097064</v>
       </c>
       <c r="B5" t="n">
-        <v>58134</v>
+        <v>58136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1107,27 +1107,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134096911</v>
+        <v>134096807</v>
       </c>
       <c r="B6" t="n">
-        <v>58519</v>
+        <v>58134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102990</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1221,10 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134097064</v>
+        <v>134096724</v>
       </c>
       <c r="B7" t="n">
-        <v>58136</v>
+        <v>58260</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1232,21 +1232,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">

--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -879,27 +879,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134096911</v>
+        <v>134096807</v>
       </c>
       <c r="B4" t="n">
-        <v>58519</v>
+        <v>58134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134097064</v>
+        <v>134096911</v>
       </c>
       <c r="B5" t="n">
-        <v>58136</v>
+        <v>58519</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134096807</v>
+        <v>134097064</v>
       </c>
       <c r="B6" t="n">
-        <v>58134</v>
+        <v>58136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,21 +1118,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -879,27 +879,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134096807</v>
+        <v>134096911</v>
       </c>
       <c r="B4" t="n">
-        <v>58134</v>
+        <v>58519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103020</v>
+        <v>102990</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134096911</v>
+        <v>134097064</v>
       </c>
       <c r="B5" t="n">
-        <v>58519</v>
+        <v>58136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102990</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1107,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134097064</v>
+        <v>134096807</v>
       </c>
       <c r="B6" t="n">
-        <v>58136</v>
+        <v>58134</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1118,21 +1118,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">

--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114071394</v>
+        <v>114071393</v>
       </c>
       <c r="B2" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>333544</v>
+        <v>333557</v>
       </c>
       <c r="R2" t="n">
-        <v>6434072</v>
+        <v>6434004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114071405</v>
+        <v>114071394</v>
       </c>
       <c r="B3" t="n">
-        <v>96610</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>333695</v>
+        <v>333544</v>
       </c>
       <c r="R3" t="n">
-        <v>6434027</v>
+        <v>6434072</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,27 +869,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134096911</v>
+        <v>134096942</v>
       </c>
       <c r="B4" t="n">
-        <v>58519</v>
+        <v>57988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102990</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -956,12 +946,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -993,60 +983,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134097064</v>
+        <v>114071398</v>
       </c>
       <c r="B5" t="n">
-        <v>58136</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hedsåsen 2, Vg</t>
+          <t>Hedsåsen, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>333627</v>
+        <v>333626</v>
       </c>
       <c r="R5" t="n">
-        <v>6434088</v>
+        <v>6433989</v>
       </c>
       <c r="S5" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,17 +1048,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,39 +1073,39 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134096807</v>
+        <v>114071401</v>
       </c>
       <c r="B6" t="n">
-        <v>58134</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1136,31 +1114,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hedsåsen 2, Vg</t>
+          <t>Hedsåsen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>333627</v>
+        <v>333645</v>
       </c>
       <c r="R6" t="n">
-        <v>6434088</v>
+        <v>6433994</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1184,17 +1150,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1209,72 +1175,64 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134096724</v>
+        <v>114271181</v>
       </c>
       <c r="B7" t="n">
-        <v>58260</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedsåsen 2, Vg</t>
+          <t>Lödöse, Hedsåsen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>333627</v>
+        <v>333784</v>
       </c>
       <c r="R7" t="n">
-        <v>6434088</v>
+        <v>6433966</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1298,17 +1256,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,22 +1286,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134096944</v>
+        <v>134096904</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>58519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,16 +1309,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>102990</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1412,12 +1375,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1449,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134096867</v>
+        <v>134096717</v>
       </c>
       <c r="B9" t="n">
-        <v>58698</v>
+        <v>58260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1460,21 +1423,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103055</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1526,12 +1489,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1563,27 +1526,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134097045</v>
+        <v>134096801</v>
       </c>
       <c r="B10" t="n">
-        <v>58624</v>
+        <v>58134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103042</v>
+        <v>103020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1640,12 +1603,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1674,6 +1637,445 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134097064</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hedsåsen 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>333627</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6434088</v>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134097031</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58624</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hedsåsen 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>333627</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6434088</v>
+      </c>
+      <c r="S12" t="n">
+        <v>100</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134096863</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58698</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hedsåsen 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>333627</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6434088</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114071405</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hedsåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>333695</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6434027</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-01-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-01-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114071393</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114071394</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134096942</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114071398</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114071401</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114271181</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134096904</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134096717</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1637,6 +1682,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134096801</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1751,6 +1801,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134097064</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1865,6 +1920,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134097031</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1979,6 +2039,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134096863</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2076,8 +2141,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114071405</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ12"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,27 +884,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114071398</v>
+        <v>134096942</v>
       </c>
       <c r="B4" t="n">
-        <v>57950</v>
+        <v>57993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -913,19 +913,31 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hedsåsen, Vg</t>
+          <t>Hedsåsen 2, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>333626</v>
+        <v>333627</v>
       </c>
       <c r="R4" t="n">
-        <v>6433989</v>
+        <v>6434088</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,17 +961,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Många träffar via birdbox, verifierad i flera appar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,24 +986,24 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114071398</t>
+          <t>https://artportalen.se/Sighting/134096942</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114071401</v>
+        <v>114071398</v>
       </c>
       <c r="B5" t="n">
         <v>57950</v>
@@ -1026,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>333645</v>
+        <v>333626</v>
       </c>
       <c r="R5" t="n">
-        <v>6433994</v>
+        <v>6433989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,13 +1104,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114071401</t>
+          <t>https://artportalen.se/Sighting/114071398</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114271181</v>
+        <v>114071401</v>
       </c>
       <c r="B6" t="n">
         <v>57950</v>
@@ -1127,23 +1139,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lödöse, Hedsåsen, Vg</t>
+          <t>Hedsåsen, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>333784</v>
+        <v>333645</v>
       </c>
       <c r="R6" t="n">
-        <v>6433966</v>
+        <v>6433994</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1167,22 +1175,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2024-01-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-01-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-01-13</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,44 +1200,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Svensson</t>
+          <t>Amanda Tas</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114271181</t>
+          <t>https://artportalen.se/Sighting/114071401</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134096904</v>
+        <v>114271181</v>
       </c>
       <c r="B7" t="n">
-        <v>58519</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1245,29 +1248,21 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hedsåsen 2, Vg</t>
+          <t>Lödöse, Hedsåsen, Vg</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>333627</v>
+        <v>333784</v>
       </c>
       <c r="R7" t="n">
-        <v>6434088</v>
+        <v>6433966</v>
       </c>
       <c r="S7" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1291,17 +1286,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+          <t>2024-01-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,27 +1316,27 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Liv Vikingson</t>
+          <t>Anna Svensson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134096904</t>
+          <t>https://artportalen.se/Sighting/114271181</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134096717</v>
+        <v>134096904</v>
       </c>
       <c r="B8" t="n">
-        <v>58260</v>
+        <v>58519</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1344,21 +1344,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103012</v>
+        <v>102990</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1446,16 +1446,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134096717</t>
+          <t>https://artportalen.se/Sighting/134096904</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134096801</v>
+        <v>134096717</v>
       </c>
       <c r="B9" t="n">
-        <v>58134</v>
+        <v>58260</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103020</v>
+        <v>103012</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1565,33 +1565,33 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134096801</t>
+          <t>https://artportalen.se/Sighting/134096717</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134097031</v>
+        <v>134096801</v>
       </c>
       <c r="B10" t="n">
-        <v>58624</v>
+        <v>58134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103042</v>
+        <v>103020</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1684,16 +1684,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134097031</t>
+          <t>https://artportalen.se/Sighting/134096801</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134096863</v>
+        <v>134097064</v>
       </c>
       <c r="B11" t="n">
-        <v>58698</v>
+        <v>58141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1701,21 +1701,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103055</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1767,12 +1767,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1803,54 +1803,66 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134096863</t>
+          <t>https://artportalen.se/Sighting/134097064</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114071405</v>
+        <v>134097031</v>
       </c>
       <c r="B12" t="n">
-        <v>97983</v>
+        <v>58624</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103042</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hedsåsen, Vg</t>
+          <t>Hedsåsen 2, Vg</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>333695</v>
+        <v>333627</v>
       </c>
       <c r="R12" t="n">
-        <v>6434027</v>
+        <v>6434088</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1874,12 +1886,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-01-13</t>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Många träffar via birdbox, verifierad i flera appar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,16 +1911,237 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Amanda Tas</t>
+          <t>Liv Vikingson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134097031</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134096863</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58698</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hedsåsen 2, Vg</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>333627</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6434088</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Många träffar via birdbox, verifierad i flera appar.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Liv Vikingson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134096863</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114071405</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hedsåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>333695</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6434027</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lilla Edet</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sankt Peder</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-01-13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-01-13</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/114071405</t>
         </is>
@@ -1922,6 +2160,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>134096942</v>
       </c>
       <c r="B4" t="n">
-        <v>57993</v>
+        <v>57995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>134097064</v>
       </c>
       <c r="B11" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>134096942</v>
       </c>
       <c r="B4" t="n">
-        <v>57995</v>
+        <v>57996</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>134097064</v>
       </c>
       <c r="B11" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>134096942</v>
       </c>
       <c r="B4" t="n">
-        <v>57996</v>
+        <v>58000</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>134097064</v>
       </c>
       <c r="B11" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 434-2024 artfynd.xlsx
+++ b/artfynd/A 434-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>134096942</v>
       </c>
       <c r="B4" t="n">
-        <v>58000</v>
+        <v>58001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
         <v>134097064</v>
       </c>
       <c r="B11" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
